--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>73.05256179600596</v>
+        <v>11.87104129185097</v>
       </c>
       <c r="D2" t="n">
-        <v>71.74983353110299</v>
+        <v>11.65934794880424</v>
       </c>
       <c r="E2" t="n">
-        <v>21.55024323382925</v>
+        <v>3.501914525497253</v>
       </c>
       <c r="F2" t="n">
-        <v>22.10245742677815</v>
+        <v>3.59164933185145</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>81.85035083625219</v>
+        <v>13.30068201089098</v>
       </c>
       <c r="D3" t="n">
-        <v>81.00032764476897</v>
+        <v>13.16255324227496</v>
       </c>
       <c r="E3" t="n">
-        <v>21.55024323382925</v>
+        <v>3.501914525497253</v>
       </c>
       <c r="F3" t="n">
-        <v>22.10245742677815</v>
+        <v>3.59164933185145</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>55.97476903567355</v>
+        <v>9.095899968296953</v>
       </c>
       <c r="D4" t="n">
-        <v>44.55895349035423</v>
+        <v>7.240829942182564</v>
       </c>
       <c r="E4" t="n">
-        <v>21.55024323382925</v>
+        <v>3.501914525497253</v>
       </c>
       <c r="F4" t="n">
-        <v>22.10245742677815</v>
+        <v>3.59164933185145</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>76.85837806530526</v>
+        <v>12.48948643561211</v>
       </c>
       <c r="D5" t="n">
-        <v>75.20577659151719</v>
+        <v>12.22093869612154</v>
       </c>
       <c r="E5" t="n">
-        <v>21.55024323382925</v>
+        <v>3.501914525497253</v>
       </c>
       <c r="F5" t="n">
-        <v>22.10245742677815</v>
+        <v>3.59164933185145</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>22.64490393395906</v>
+        <v>3.679796889268348</v>
       </c>
       <c r="D6" t="n">
-        <v>22.60148163363336</v>
+        <v>3.672740765465421</v>
       </c>
       <c r="E6" t="n">
-        <v>21.55024323382925</v>
+        <v>3.501914525497253</v>
       </c>
       <c r="F6" t="n">
-        <v>22.10245742677815</v>
+        <v>3.59164933185145</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
